--- a/stories/arbres/ATOM-SEC.PAR.001-03.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Noé arrive à la cour d'école avec maman. Maman montre un espace. C'est près des plots bleus. Maman dit : tu joues ici, dans l'espace montré. Ici, l'adulte voit. Noé prend un plot. Il le pose. Il fait un petit chemin. Maman s'assoit sur le muret. Parce que Noé reste dans l'espace montré, maman le voit. Noé revient près d'elle. Maman dit : je te vois. L'adulte voit. Plus tard, ils vont au parc. Maman montre un autre espace. C'est près du bac à sable. Maman dit : tu joues ici. L'espace montré. Ici, l'adulte voit. Noé se souvient. Il reste près du bac. Il verse le sable. Le sable est frais. Il revient vers le banc. Maman dit : tu as repris la règle. Même leçon, autre lieu. Noé sourit. Il reste dans l'espace montré. L'adulte voit.</t>
+          <t>Noé arrive à la cour d'école avec maman. Maman montre un espace. C'est près des plots bleus. Tu joues ici, dans l'espace montré. Ici, l'adulte voit. Noé prend un plot. Il le pose. Il fait un petit chemin. Maman s'assoit sur le muret. Parce que Noé reste dans l'espace montré, maman le voit. Noé revient près d'elle. Je te vois. L'adulte voit. Plus tard, ils vont au parc. Maman montre un autre espace. C'est près du bac à sable. Tu joues ici. L'espace montré. Ici, l'adulte voit. Noé se souvient. Il reste près du bac. Il verse le sable. Le sable est frais. Il revient vers le banc. Tu as repris la règle. Même leçon, autre lieu. Noé sourit. Il reste dans l'espace montré. L'adulte voit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Noé arrive à la cour d'école avec maman. Maman montre un espace. C'est près des plots bleus.
+maman|Tu joues ici, dans l'espace montré. Ici, l'adulte voit.
+narrateur|Noé prend un plot. Il le pose. Il fait un petit chemin. Maman s'assoit sur le muret. Parce que Noé reste dans l'espace montré, maman le voit. Noé revient près d'elle.
+maman|Je te vois. L'adulte voit. Plus tard, ils vont au parc. Maman montre un autre espace. C'est près du bac à sable.
+maman|Tu joues ici. L'espace montré. Ici, l'adulte voit.
+narrateur|Noé se souvient. Il reste près du bac. Il verse le sable. Le sable est frais. Il revient vers le banc.
+maman|Tu as repris la règle. Même leçon, autre lieu.
+narrateur|Noé sourit. Il reste dans l'espace montré. L'adulte voit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Noé joue. Où reste-t-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1666,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Noé est resté dans l'espace montré. À la cour, puis au parc. L'adulte voyait.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1829,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Noé range le seau. Maman lui tend la gourde.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1996,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-03.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,11 @@
 narrateur|Noé sourit. Il reste dans l'espace montré. L'adulte voit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1510,7 @@
           <t>narrateur|Noé joue. Où reste-t-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1671,6 +1682,11 @@
           <t>narrateur|Noé est resté dans l'espace montré. À la cour, puis au parc. L'adulte voyait.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1850,7 @@
           <t>narrateur|Noé range le seau. Maman lui tend la gourde.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2018,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2061,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2276,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.PAR.001-03.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Noé reste où maman voit</t>
+          <t>Les plots bleus d'Aniss</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Aniss pose des plots bleus dans la cour. Plus tard, au parc, il reste près du bac. Même règle : l'espace montré, l'adulte voit.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Noé arrive à la cour d'école avec maman. Maman montre un espace. C'est près des plots bleus. Tu joues ici, dans l'espace montré. Ici, l'adulte voit. Noé prend un plot. Il le pose. Il fait un petit chemin. Maman s'assoit sur le muret. Parce que Noé reste dans l'espace montré, maman le voit. Noé revient près d'elle. Je te vois. L'adulte voit. Plus tard, ils vont au parc. Maman montre un autre espace. C'est près du bac à sable. Tu joues ici. L'espace montré. Ici, l'adulte voit. Noé se souvient. Il reste près du bac. Il verse le sable. Le sable est frais. Il revient vers le banc. Tu as repris la règle. Même leçon, autre lieu. Noé sourit. Il reste dans l'espace montré. L'adulte voit.</t>
+          <t>De la craie blanche poudre les plots bleus. La poussière colle aux doigts. Le muret de la cour est chaud. Une cloche a sonné, tout à l'heure. Le sac de maman sent la pomme. Une pomme rouge brille dans le filet. Tu as vu la poussière, Aniss ? Elle est blanche, maman. Oui. C'est de la craie. Aniss souffle un peu. Un nuage blanc s'envole. Ça pique le nez. Un peu, oui. En ce moment, maman montre un espace. C'est près des plots bleus. Tu joues ici, dans l'espace montré. Ici, l'adulte voit. Aniss prend un plot. Le plastique est un peu rêche. Il le pose. Il fait un petit chemin bleu. Maman s'assoit sur le muret. Parce qu'Aniss reste dans l'espace montré, maman le voit. L'adulte voit. Un chemin, maman. Je le vois. Tu restes dans l'espace montré ? Oui. Bravo. Aniss pose encore deux plots. Le chemin bleu s'allonge un peu. Aniss revient près d'elle. Je te vois. L'adulte voit. Plus tard, ils vont au parc. Le chemin sent l'herbe coupée. Une abeille passe près d'une fleur. Elle fait un petit zzz. Tu as entendu ? Zzz. Maman montre un autre espace. C'est près du bac à sable. Tu joues ici. L'espace montré. Ici, l'adulte voit. Aniss se souvient. Il reste près du bac. Il verse le sable. Le sable est frais. Il est frais, comme la craie. Oui. Tu as repris la règle. Même leçon, autre lieu. Aniss tasse un gâteau. Il revient vers le banc. Tu as fait du bon travail. Dans l'espace montré. Oui. L'adulte voit. Aniss sourit. Un peu de craie reste sur son pouce.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,68 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Noé arrive à la cour d'école avec maman. Maman montre un espace. C'est près des plots bleus.
-maman|Tu joues ici, dans l'espace montré. Ici, l'adulte voit.
-narrateur|Noé prend un plot. Il le pose. Il fait un petit chemin. Maman s'assoit sur le muret. Parce que Noé reste dans l'espace montré, maman le voit. Noé revient près d'elle.
-maman|Je te vois. L'adulte voit. Plus tard, ils vont au parc. Maman montre un autre espace. C'est près du bac à sable.
-maman|Tu joues ici. L'espace montré. Ici, l'adulte voit.
-narrateur|Noé se souvient. Il reste près du bac. Il verse le sable. Le sable est frais. Il revient vers le banc.
-maman|Tu as repris la règle. Même leçon, autre lieu.
-narrateur|Noé sourit. Il reste dans l'espace montré. L'adulte voit.</t>
+          <t>narrateur|De la craie blanche poudre les plots bleus.
+narrateur|La poussière colle aux doigts.
+narrateur|Le muret de la cour est chaud.
+narrateur|Une cloche a sonné, tout à l'heure.
+narrateur|Le sac de maman sent la pomme.
+narrateur|Une pomme rouge brille dans le filet.
+maman|Tu as vu la poussière, Aniss ?
+enfant-m|Elle est blanche, maman.
+maman|Oui.
+maman|C'est de la craie.
+narrateur|Aniss souffle un peu.
+narrateur|Un nuage blanc s'envole.
+enfant-m|Ça pique le nez.
+maman|Un peu, oui.
+narrateur|En ce moment, maman montre un espace.
+narrateur|C'est près des plots bleus.
+maman|Tu joues ici, dans l'espace montré.
+maman|Ici, l'adulte voit.
+narrateur|Aniss prend un plot.
+narrateur|Le plastique est un peu rêche.
+narrateur|Il le pose.
+narrateur|Il fait un petit chemin bleu.
+narrateur|Maman s'assoit sur le muret.
+narrateur|Parce qu'Aniss reste dans l'espace montré, maman le voit.
+narrateur|L'adulte voit.
+enfant-m|Un chemin, maman.
+maman|Je le vois.
+maman|Tu restes dans l'espace montré ?
+enfant-m|Oui.
+maman|Bravo.
+narrateur|Aniss pose encore deux plots.
+narrateur|Le chemin bleu s'allonge un peu.
+narrateur|Aniss revient près d'elle.
+maman|Je te vois.
+maman|L'adulte voit.
+narrateur|Plus tard, ils vont au parc.
+narrateur|Le chemin sent l'herbe coupée.
+narrateur|Une abeille passe près d'une fleur.
+narrateur|Elle fait un petit zzz.
+maman|Tu as entendu ?
+enfant-m|Zzz.
+narrateur|Maman montre un autre espace.
+narrateur|C'est près du bac à sable.
+maman|Tu joues ici.
+maman|L'espace montré.
+maman|Ici, l'adulte voit.
+narrateur|Aniss se souvient.
+narrateur|Il reste près du bac.
+narrateur|Il verse le sable.
+narrateur|Le sable est frais.
+enfant-m|Il est frais, comme la craie.
+maman|Oui.
+maman|Tu as repris la règle.
+maman|Même leçon, autre lieu.
+narrateur|Aniss tasse un gâteau.
+narrateur|Il revient vers le banc.
+maman|Tu as fait du bon travail.
+enfant-m|Dans l'espace montré.
+maman|Oui.
+maman|L'adulte voit.
+narrateur|Aniss sourit.
+narrateur|Un peu de craie reste sur son pouce.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1351,7 +1417,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Noé joue. Où reste-t-il ?</t>
+          <t>Aniss joue. Où reste-t-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1507,10 +1573,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Noé joue. Où reste-t-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Aniss joue.
+narrateur|Où reste-t-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1535,7 +1601,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Noé est resté dans l'espace montré. À la cour, puis au parc. L'adulte voyait.</t>
+          <t>Aniss est resté dans l'espace montré. À la cour, puis au parc. L'adulte voyait. Tu es resté dans l'espace montré ? Oui. Les plots, puis le bac. Bravo. Je te voyais. Le plot bleu a un peu de craie. Le seau a un peu de sable.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1679,7 +1745,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Noé est resté dans l'espace montré. À la cour, puis au parc. L'adulte voyait.</t>
+          <t>narrateur|Aniss est resté dans l'espace montré.
+narrateur|À la cour, puis au parc.
+narrateur|L'adulte voyait.
+maman|Tu es resté dans l'espace montré ?
+enfant-m|Oui.
+enfant-m|Les plots, puis le bac.
+maman|Bravo.
+maman|Je te voyais.
+narrateur|Le plot bleu a un peu de craie.
+narrateur|Le seau a un peu de sable.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1711,7 +1786,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Noé range le seau. Maman lui tend la gourde.</t>
+          <t>Aniss range le seau. Maman lui tend la gourde. La pomme du sac sent encore. Tu as soif ? Oui, maman. Bois. Tu as repris la règle au parc. L'espace montré. Oui. L'adulte voit. Bravo, Aniss. Aniss boit. Une goutte coule sur son menton.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1847,10 +1922,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Noé range le seau. Maman lui tend la gourde.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Aniss range le seau.
+narrateur|Maman lui tend la gourde.
+narrateur|La pomme du sac sent encore.
+maman|Tu as soif ?
+enfant-m|Oui, maman.
+maman|Bois.
+maman|Tu as repris la règle au parc.
+enfant-m|L'espace montré.
+maman|Oui.
+maman|L'adulte voit.
+maman|Bravo, Aniss.
+narrateur|Aniss boit.
+narrateur|Une goutte coule sur son menton.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1875,7 +1961,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Les plots bleus restent dans la cour. J'ai fait un chemin. Oui. Puis un gâteau de sable. Dans l'espace montré. Bravo, Aniss. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2015,10 +2101,15 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Les plots bleus restent dans la cour.
+enfant-m|J'ai fait un chemin.
+maman|Oui.
+maman|Puis un gâteau de sable.
+maman|Dans l'espace montré.
+maman|Bravo, Aniss.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2037,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2075,6 +2166,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-03.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-03.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>De la craie blanche poudre les plots bleus. La poussière colle aux doigts. Le muret de la cour est chaud. Une cloche a sonné, tout à l'heure. Le sac de maman sent la pomme. Une pomme rouge brille dans le filet. Tu as vu la poussière, Aniss ? Elle est blanche, maman. Oui. C'est de la craie. Aniss souffle un peu. Un nuage blanc s'envole. Ça pique le nez. Un peu, oui. En ce moment, maman montre un espace. C'est près des plots bleus. Tu joues ici, dans l'espace montré. Ici, l'adulte voit. Aniss prend un plot. Le plastique est un peu rêche. Il le pose. Il fait un petit chemin bleu. Maman s'assoit sur le muret. Parce qu'Aniss reste dans l'espace montré, maman le voit. L'adulte voit. Un chemin, maman. Je le vois. Tu restes dans l'espace montré ? Oui. Bravo. Aniss pose encore deux plots. Le chemin bleu s'allonge un peu. Aniss revient près d'elle. Je te vois. L'adulte voit. Plus tard, ils vont au parc. Le chemin sent l'herbe coupée. Une abeille passe près d'une fleur. Elle fait un petit zzz. Tu as entendu ? Zzz. Maman montre un autre espace. C'est près du bac à sable. Tu joues ici. L'espace montré. Ici, l'adulte voit. Aniss se souvient. Il reste près du bac. Il verse le sable. Le sable est frais. Il est frais, comme la craie. Oui. Tu as repris la règle. Même leçon, autre lieu. Aniss tasse un gâteau. Il revient vers le banc. Tu as fait du bon travail. Dans l'espace montré. Oui. L'adulte voit. Aniss sourit. Un peu de craie reste sur son pouce.</t>
+          <t>De la craie blanche poudre les plots bleus. La poussière colle aux doigts. Le muret de la cour est chaud. Une cloche a sonné, tout à l'heure. Le sac de maman sent la pomme. Une pomme rouge brille dans le filet. Tu as vu la poussière, Aniss ? Elle est blanche, maman. Oui. C'est de la craie. Aniss souffle un peu. Un nuage blanc s'envole. Ça pique le nez. Un peu, oui. En ce moment, maman montre un espace. C'est près des plots bleus. Tu joues ici, dans l'espace montré. Ici, l'adulte voit. Aniss prend un plot. Le plastique est un peu rêche. Il le pose. Il fait un petit chemin bleu. Maman s'assoit sur le muret. Parce qu'Aniss reste dans l'espace montré, maman le voit. L'adulte voit. Un chemin, maman. Je le vois. Tu restes dans l'espace montré ? Oui. Bravo. Aniss pose encore deux plots. Le chemin bleu s'allonge un peu. Aniss revient près d'elle. Je te vois. L'adulte voit. Plus tard, ils vont au parc. Le chemin sent l'herbe coupée. Une abeille passe près d'une fleur. Elle fait un petit zzz. Tu as entendu ? Zzz. Maman montre un autre espace. C'est près du bac à sable. Tu joues ici. L'espace montré. Ici, l'adulte voit. Aniss se souvient. Il reste près du bac. Il verse le sable. Le sable est frais. Il est frais, comme la craie. Oui. Tu as repris la règle. Même leçon, autre lieu. Aniss tasse un gâteau. Il revient vers le banc. Dans l'espace montré. Oui. L'adulte voit. Aniss sourit. Un peu de craie reste sur son pouce.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Noé arrive à la cour d'école avec maman. Maman montre un &lt;emphasis level="moderate"&gt;espace&lt;/emphasis&gt;. C'est près des plots bleus. Maman dit : tu joues ici, dans l'espace montré. Ici, l'adulte voit. Noé prend un plot. Il le pose. Il fait un petit chemin. Maman s'assoit sur le muret. Parce que Noé reste dans l'espace montré, maman le voit. Noé revient près d'elle. Maman dit : je te vois. L'adulte voit. Plus tard, ils vont au parc. Maman montre un autre espace. C'est près du bac à sable. Maman dit : tu joues ici. L'espace montré. Ici, l'adulte voit. Noé se souvient. Il reste près du bac. Il verse le sable. Le sable est frais. Il revient vers le banc. Maman dit : tu as repris la règle. Même leçon, autre lieu. Noé sourit. Il reste dans l'espace montré. L'adulte voit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>De la craie blanche poudre les plots bleus. La poussière colle aux doigts. Le muret de la cour est chaud. Une cloche a sonné, tout à l'heure. Le sac de maman sent la pomme. Une pomme rouge brille dans le filet. Tu as vu la poussière, Aniss ? Elle est blanche, maman. Oui. C'est de la craie. Aniss souffle un peu. Un nuage blanc s'envole. Ça pique le nez. Un peu, oui. En ce moment, maman montre un espace. C'est près des plots bleus. Tu joues ici, dans l'espace montré. Ici, l'adulte voit. Aniss prend un plot. Le plastique est un peu rêche. Il le pose. Il fait un petit chemin bleu. Maman s'assoit sur le muret. Parce qu'Aniss reste dans l'espace montré, maman le voit. L'adulte voit. Un chemin, maman. Je le vois. Tu restes dans l'espace montré ? Oui. Bravo. Aniss pose encore deux plots. Le chemin bleu s'allonge un peu. Aniss revient près d'elle. Je te vois. L'adulte voit. Plus tard, ils vont au parc. Le chemin sent l'herbe coupée. Une abeille passe près d'une fleur. Elle fait un petit zzz. Tu as entendu ? Zzz. Maman montre un autre espace. C'est près du bac à sable. Tu joues ici. L'espace montré. Ici, l'adulte voit. Aniss se souvient. Il reste près du bac. Il verse le sable. Le sable est frais. Il est frais, comme la craie. Oui. Tu as repris la règle. Même leçon, autre lieu. Aniss tasse un gâteau. Il revient vers le banc. Dans l'espace montré. Oui. L'adulte voit. Aniss sourit. Un peu de craie reste sur son pouce.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1380,7 +1380,6 @@
 maman|Même leçon, autre lieu.
 narrateur|Aniss tasse un gâteau.
 narrateur|Il revient vers le banc.
-maman|Tu as fait du bon travail.
 enfant-m|Dans l'espace montré.
 maman|Oui.
 maman|L'adulte voit.
@@ -1422,7 +1421,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Noé joue. Où reste-t-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss joue. Où reste-t-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1606,7 +1605,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Noé est resté dans l'&lt;emphasis level="moderate"&gt;espace&lt;/emphasis&gt; montré. À la cour, puis au parc. L'adulte voyait.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss est resté dans l'espace montré. À la cour, puis au parc. L'adulte voyait. Tu es resté dans l'espace montré ? Oui. Les plots, puis le bac. Bravo. Je te voyais. Le plot bleu a un peu de craie. Le seau a un peu de sable.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1791,7 +1790,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Noé range le seau. Maman lui tend la gourde.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss range le seau. Maman lui tend la gourde. La pomme du sac sent encore. Tu as soif ? Oui, maman. Bois. Tu as repris la règle au parc. L'espace montré. Oui. L'adulte voit. Bravo, Aniss. Aniss boit. Une goutte coule sur son menton.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1961,12 +1960,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Les plots bleus restent dans la cour. J'ai fait un chemin. Oui. Puis un gâteau de sable. Dans l'espace montré. Bravo, Aniss. L'histoire est finie.</t>
+          <t>Les plots bleus restent dans la cour. J'ai fait un chemin. Oui. Puis un gâteau de sable. Dans l'espace montré. Bravo, Aniss.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les plots bleus restent dans la cour. J'ai fait un chemin. Oui. Puis un gâteau de sable. Dans l'espace montré. Bravo, Aniss.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2106,8 +2105,7 @@
 maman|Oui.
 maman|Puis un gâteau de sable.
 maman|Dans l'espace montré.
-maman|Bravo, Aniss.
-narrateur|L'histoire est finie.</t>
+maman|Bravo, Aniss.</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2173,6 +2171,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-03.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-03.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Noé, maman</t>
+          <t>Aniss, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-03.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-03.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Les plots bleus d'Aniss</t>
+          <t>Le bateau de noix d'Aniss</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cour d'école puis parc</t>
+          <t>square du village, fontaine, tilleuls après le marché</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aniss pose des plots bleus dans la cour. Plus tard, au parc, il reste près du bac. Même règle : l'espace montré, l'adulte voit.</t>
+          <t>Aniss veut faire traverser son bateau de noix. Un papier roule vers la haie. Maman devient petite. Il revient parce que le bateau est avec elle.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>De la craie blanche poudre les plots bleus. La poussière colle aux doigts. Le muret de la cour est chaud. Une cloche a sonné, tout à l'heure. Le sac de maman sent la pomme. Une pomme rouge brille dans le filet. Tu as vu la poussière, Aniss ? Elle est blanche, maman. Oui. C'est de la craie. Aniss souffle un peu. Un nuage blanc s'envole. Ça pique le nez. Un peu, oui. En ce moment, maman montre un espace. C'est près des plots bleus. Tu joues ici, dans l'espace montré. Ici, l'adulte voit. Aniss prend un plot. Le plastique est un peu rêche. Il le pose. Il fait un petit chemin bleu. Maman s'assoit sur le muret. Parce qu'Aniss reste dans l'espace montré, maman le voit. L'adulte voit. Un chemin, maman. Je le vois. Tu restes dans l'espace montré ? Oui. Bravo. Aniss pose encore deux plots. Le chemin bleu s'allonge un peu. Aniss revient près d'elle. Je te vois. L'adulte voit. Plus tard, ils vont au parc. Le chemin sent l'herbe coupée. Une abeille passe près d'une fleur. Elle fait un petit zzz. Tu as entendu ? Zzz. Maman montre un autre espace. C'est près du bac à sable. Tu joues ici. L'espace montré. Ici, l'adulte voit. Aniss se souvient. Il reste près du bac. Il verse le sable. Le sable est frais. Il est frais, comme la craie. Oui. Tu as repris la règle. Même leçon, autre lieu. Aniss tasse un gâteau. Il revient vers le banc. Dans l'espace montré. Oui. L'adulte voit. Aniss sourit. Un peu de craie reste sur son pouce.</t>
+          <t>Les tilleuls du square sentent le miel. Une caisse vide sent encore la pêche. L'eau de la fontaine tremble au soleil. Le pain du sac de maman est encore tiède. Une coque de noix attend près du bord. Tu as vu l'eau, Aniss ? Elle brille, maman. Elle est froide, un peu. Une feuille jaune fait un tout petit voile. Aniss la pique dans la noix. Je veux qu'il traverse. Jusqu'à l'autre bord. On le pose ici, près de moi ? Oui. En ce moment, la coque touche l'eau. L'eau pique les doigts, toute vive. Il flotte ! Tout doux, avec le doigt. Aniss pousse le voile d'un ongle. Le bateau part, puis il tourne. Une abeille passe au-dessus des tilleuls. Zzz. Tu l'entends ? Oui. Un papier du marché s'envole un peu. Il roule vers la haie, tout au fond. Je le prends ! Aniss fait trois pas vers la haie. La fontaine devient petite derrière lui. Maman devient une petite forme. Le bateau de noix reste près d'elle. Le voile jaune penche, tout seul. Mon bateau est là. Aniss revient vers l'eau. Les dalles sont chaudes sous ses pieds. Tu reviens près du bateau ? Oui. Il va partir sans moi. Je te vois mieux, ici. Le voile se redresse sous le doigt. La coque avance, toute lente. Il va arriver. Je le vois, et je te vois. Une goutte saute sur le genou d'Aniss. Elle est froide. Comme l'eau de la noix. Le bateau touche l'autre bord. Il a traversé ! Bravo. Il est resté avec nous. Aniss reprend la coque, tout prudent. La noix est luisante, un peu froide. On goûte le pain, après ? Oui, maman. Le sac sent le blé chaud. Une miette tombe près de l'eau.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>De la craie blanche poudre les plots bleus. La poussière colle aux doigts. Le muret de la cour est chaud. Une cloche a sonné, tout à l'heure. Le sac de maman sent la pomme. Une pomme rouge brille dans le filet. Tu as vu la poussière, Aniss ? Elle est blanche, maman. Oui. C'est de la craie. Aniss souffle un peu. Un nuage blanc s'envole. Ça pique le nez. Un peu, oui. En ce moment, maman montre un espace. C'est près des plots bleus. Tu joues ici, dans l'espace montré. Ici, l'adulte voit. Aniss prend un plot. Le plastique est un peu rêche. Il le pose. Il fait un petit chemin bleu. Maman s'assoit sur le muret. Parce qu'Aniss reste dans l'espace montré, maman le voit. L'adulte voit. Un chemin, maman. Je le vois. Tu restes dans l'espace montré ? Oui. Bravo. Aniss pose encore deux plots. Le chemin bleu s'allonge un peu. Aniss revient près d'elle. Je te vois. L'adulte voit. Plus tard, ils vont au parc. Le chemin sent l'herbe coupée. Une abeille passe près d'une fleur. Elle fait un petit zzz. Tu as entendu ? Zzz. Maman montre un autre espace. C'est près du bac à sable. Tu joues ici. L'espace montré. Ici, l'adulte voit. Aniss se souvient. Il reste près du bac. Il verse le sable. Le sable est frais. Il est frais, comme la craie. Oui. Tu as repris la règle. Même leçon, autre lieu. Aniss tasse un gâteau. Il revient vers le banc. Dans l'espace montré. Oui. L'adulte voit. Aniss sourit. Un peu de craie reste sur son pouce.</t>
+          <t>Les tilleuls du square sentent le miel. Une caisse vide sent encore la pêche. L'eau de la fontaine tremble au soleil. Le pain du sac de maman est encore tiède. Une coque de noix attend près du bord. Tu as vu l'eau, Aniss ? Elle brille, maman. Elle est froide, un peu. Une feuille jaune fait un tout petit voile. Aniss la pique dans la noix. Je veux qu'il traverse. Jusqu'à l'autre bord. On le pose ici, près de moi ? Oui. En ce moment, la coque touche l'eau. L'eau pique les doigts, toute vive. Il flotte ! Tout doux, avec le doigt. Aniss pousse le voile d'un ongle. Le bateau part, puis il tourne. Une abeille passe au-dessus des tilleuls. Zzz. Tu l'entends ? Oui. Un papier du marché s'envole un peu. Il roule vers la haie, tout au fond. Je le prends ! Aniss fait trois pas vers la haie. La fontaine devient petite derrière lui. Maman devient une petite forme. Le bateau de noix reste près d'elle. Le voile jaune penche, tout seul. Mon bateau est là. Aniss revient vers l'eau. Les dalles sont chaudes sous ses pieds. Tu reviens près du bateau ? Oui. Il va partir sans moi. Je te vois mieux, ici. Le voile se redresse sous le doigt. La coque avance, toute lente. Il va arriver. Je le vois, et je te vois. Une goutte saute sur le genou d'Aniss. Elle est froide. Comme l'eau de la noix. Le bateau touche l'autre bord. Il a traversé ! Bravo. Il est resté avec nous. Aniss reprend la coque, tout prudent. La noix est luisante, un peu froide. On goûte le pain, après ? Oui, maman. Le sac sent le blé chaud. Une miette tombe près de l'eau.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1324,67 +1324,62 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|De la craie blanche poudre les plots bleus.
-narrateur|La poussière colle aux doigts.
-narrateur|Le muret de la cour est chaud.
-narrateur|Une cloche a sonné, tout à l'heure.
-narrateur|Le sac de maman sent la pomme.
-narrateur|Une pomme rouge brille dans le filet.
-maman|Tu as vu la poussière, Aniss ?
-enfant-m|Elle est blanche, maman.
-maman|Oui.
-maman|C'est de la craie.
-narrateur|Aniss souffle un peu.
-narrateur|Un nuage blanc s'envole.
-enfant-m|Ça pique le nez.
-maman|Un peu, oui.
-narrateur|En ce moment, maman montre un espace.
-narrateur|C'est près des plots bleus.
-maman|Tu joues ici, dans l'espace montré.
-maman|Ici, l'adulte voit.
-narrateur|Aniss prend un plot.
-narrateur|Le plastique est un peu rêche.
-narrateur|Il le pose.
-narrateur|Il fait un petit chemin bleu.
-narrateur|Maman s'assoit sur le muret.
-narrateur|Parce qu'Aniss reste dans l'espace montré, maman le voit.
-narrateur|L'adulte voit.
-enfant-m|Un chemin, maman.
-maman|Je le vois.
-maman|Tu restes dans l'espace montré ?
+          <t>narrateur|Les tilleuls du square sentent le miel.
+narrateur|Une caisse vide sent encore la pêche.
+narrateur|L'eau de la fontaine tremble au soleil.
+narrateur|Le pain du sac de maman est encore tiède.
+narrateur|Une coque de noix attend près du bord.
+maman|Tu as vu l'eau, Aniss ?
+enfant-m|Elle brille, maman.
+maman|Elle est froide, un peu.
+narrateur|Une feuille jaune fait un tout petit voile.
+narrateur|Aniss la pique dans la noix.
+enfant-m|Je veux qu'il traverse.
+enfant-m|Jusqu'à l'autre bord.
+maman|On le pose ici, près de moi ?
 enfant-m|Oui.
+narrateur|En ce moment, la coque touche l'eau.
+narrateur|L'eau pique les doigts, toute vive.
+enfant-m|Il flotte !
+maman|Tout doux, avec le doigt.
+narrateur|Aniss pousse le voile d'un ongle.
+narrateur|Le bateau part, puis il tourne.
+narrateur|Une abeille passe au-dessus des tilleuls.
+enfant-m|Zzz.
+maman|Tu l'entends ?
+enfant-m|Oui.
+narrateur|Un papier du marché s'envole un peu.
+narrateur|Il roule vers la haie, tout au fond.
+enfant-m|Je le prends !
+narrateur|Aniss fait trois pas vers la haie.
+narrateur|La fontaine devient petite derrière lui.
+narrateur|Maman devient une petite forme.
+narrateur|Le bateau de noix reste près d'elle.
+narrateur|Le voile jaune penche, tout seul.
+enfant-m|Mon bateau est là.
+narrateur|Aniss revient vers l'eau.
+narrateur|Les dalles sont chaudes sous ses pieds.
+maman|Tu reviens près du bateau ?
+enfant-m|Oui.
+enfant-m|Il va partir sans moi.
+maman|Je te vois mieux, ici.
+narrateur|Le voile se redresse sous le doigt.
+narrateur|La coque avance, toute lente.
+enfant-m|Il va arriver.
+maman|Je le vois, et je te vois.
+narrateur|Une goutte saute sur le genou d'Aniss.
+enfant-m|Elle est froide.
+maman|Comme l'eau de la noix.
+narrateur|Le bateau touche l'autre bord.
+enfant-m|Il a traversé !
 maman|Bravo.
-narrateur|Aniss pose encore deux plots.
-narrateur|Le chemin bleu s'allonge un peu.
-narrateur|Aniss revient près d'elle.
-maman|Je te vois.
-maman|L'adulte voit.
-narrateur|Plus tard, ils vont au parc.
-narrateur|Le chemin sent l'herbe coupée.
-narrateur|Une abeille passe près d'une fleur.
-narrateur|Elle fait un petit zzz.
-maman|Tu as entendu ?
-enfant-m|Zzz.
-narrateur|Maman montre un autre espace.
-narrateur|C'est près du bac à sable.
-maman|Tu joues ici.
-maman|L'espace montré.
-maman|Ici, l'adulte voit.
-narrateur|Aniss se souvient.
-narrateur|Il reste près du bac.
-narrateur|Il verse le sable.
-narrateur|Le sable est frais.
-enfant-m|Il est frais, comme la craie.
-maman|Oui.
-maman|Tu as repris la règle.
-maman|Même leçon, autre lieu.
-narrateur|Aniss tasse un gâteau.
-narrateur|Il revient vers le banc.
-enfant-m|Dans l'espace montré.
-maman|Oui.
-maman|L'adulte voit.
-narrateur|Aniss sourit.
-narrateur|Un peu de craie reste sur son pouce.</t>
+maman|Il est resté avec nous.
+narrateur|Aniss reprend la coque, tout prudent.
+narrateur|La noix est luisante, un peu froide.
+maman|On goûte le pain, après ?
+enfant-m|Oui, maman.
+narrateur|Le sac sent le blé chaud.
+narrateur|Une miette tombe près de l'eau.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1416,12 +1411,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Aniss joue. Où reste-t-il ?</t>
+          <t>Aniss joue près de l'eau. Où reste-t-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Aniss joue. Où reste-t-il ?</t>
+          <t>Aniss joue près de l'eau. Où reste-t-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1436,7 +1431,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>espace montré | près maman | le bac | où maman voit | ici</t>
+          <t>espace montré | près maman | près de maman | le bateau | où maman voit | ici</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1451,7 +1446,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Maman a montré un espace. L'adulte voit. Où reste Noé ?</t>
+          <t>Le bateau est près de maman. Où reste Aniss ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1493,14 +1488,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1572,7 +1567,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Aniss joue.
+          <t>narrateur|Aniss joue près de l'eau.
 narrateur|Où reste-t-il ?</t>
         </is>
       </c>
@@ -1600,12 +1595,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aniss est resté dans l'espace montré. À la cour, puis au parc. L'adulte voyait. Tu es resté dans l'espace montré ? Oui. Les plots, puis le bac. Bravo. Je te voyais. Le plot bleu a un peu de craie. Le seau a un peu de sable.</t>
+          <t>Le papier reste coincé dans la haie. Aniss ne va pas le chercher. Il tient encore la noix mouillée. Le bateau est avec moi, tu vois ? Oui. Alors je reste. Je te vois, près de la fontaine. Une feuille neuve sert de voile. Aniss la pique, tout doux. Encore une traversée. Ici, je te vois bien. Le square sent le miel et le pain. L'eau cliquette contre la pierre. Il tourne encore. Tu le pousses du doigt ? Du tout petit doigt. La coque file vers le bord. Maman la suit des yeux, et Aniss aussi.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Aniss est resté dans l'espace montré. À la cour, puis au parc. L'adulte voyait. Tu es resté dans l'espace montré ? Oui. Les plots, puis le bac. Bravo. Je te voyais. Le plot bleu a un peu de craie. Le seau a un peu de sable.</t>
+          <t>Le papier reste coincé dans la haie. Aniss ne va pas le chercher. Il tient encore la noix mouillée. Le bateau est avec moi, tu vois ? Oui. Alors je reste. Je te vois, près de la fontaine. Une feuille neuve sert de voile. Aniss la pique, tout doux. Encore une traversée. Ici, je te vois bien. Le square sent le miel et le pain. L'eau cliquette contre la pierre. Il tourne encore. Tu le pousses du doigt ? Du tout petit doigt. La coque file vers le bord. Maman la suit des yeux, et Aniss aussi.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1668,7 +1663,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1744,16 +1739,24 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Aniss est resté dans l'espace montré.
-narrateur|À la cour, puis au parc.
-narrateur|L'adulte voyait.
-maman|Tu es resté dans l'espace montré ?
+          <t>narrateur|Le papier reste coincé dans la haie.
+narrateur|Aniss ne va pas le chercher.
+narrateur|Il tient encore la noix mouillée.
+maman|Le bateau est avec moi, tu vois ?
 enfant-m|Oui.
-enfant-m|Les plots, puis le bac.
-maman|Bravo.
-maman|Je te voyais.
-narrateur|Le plot bleu a un peu de craie.
-narrateur|Le seau a un peu de sable.</t>
+enfant-m|Alors je reste.
+maman|Je te vois, près de la fontaine.
+narrateur|Une feuille neuve sert de voile.
+narrateur|Aniss la pique, tout doux.
+enfant-m|Encore une traversée.
+maman|Ici, je te vois bien.
+narrateur|Le square sent le miel et le pain.
+narrateur|L'eau cliquette contre la pierre.
+enfant-m|Il tourne encore.
+maman|Tu le pousses du doigt ?
+enfant-m|Du tout petit doigt.
+narrateur|La coque file vers le bord.
+narrateur|Maman la suit des yeux, et Aniss aussi.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1785,12 +1788,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Aniss range le seau. Maman lui tend la gourde. La pomme du sac sent encore. Tu as soif ? Oui, maman. Bois. Tu as repris la règle au parc. L'espace montré. Oui. L'adulte voit. Bravo, Aniss. Aniss boit. Une goutte coule sur son menton.</t>
+          <t>Maman rompt le pain tiède. Une miette reste sur le pouce d'Aniss. Tu as soif ? Un peu. La gourde est fraîche contre la joue. Le bateau a traversé. Oui. Il était là, avec nous. Aniss essuie la noix sur sa manche. La manche sent le tilleul. On la pose dans le sac ? Près du pain. Le square s'ombre un peu. Les tilleuls bougent, tout lents.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Aniss range le seau. Maman lui tend la gourde. La pomme du sac sent encore. Tu as soif ? Oui, maman. Bois. Tu as repris la règle au parc. L'espace montré. Oui. L'adulte voit. Bravo, Aniss. Aniss boit. Une goutte coule sur son menton.</t>
+          <t>Maman rompt le pain tiède. Une miette reste sur le pouce d'Aniss. Tu as soif ? Un peu. La gourde est fraîche contre la joue. Le bateau a traversé. Oui. Il était là, avec nous. Aniss essuie la noix sur sa manche. La manche sent le tilleul. On la pose dans le sac ? Près du pain. Le square s'ombre un peu. Les tilleuls bougent, tout lents.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1853,7 +1856,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1921,19 +1924,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Aniss range le seau.
-narrateur|Maman lui tend la gourde.
-narrateur|La pomme du sac sent encore.
+          <t>narrateur|Maman rompt le pain tiède.
+narrateur|Une miette reste sur le pouce d'Aniss.
 maman|Tu as soif ?
-enfant-m|Oui, maman.
-maman|Bois.
-maman|Tu as repris la règle au parc.
-enfant-m|L'espace montré.
+enfant-m|Un peu.
+narrateur|La gourde est fraîche contre la joue.
+enfant-m|Le bateau a traversé.
 maman|Oui.
-maman|L'adulte voit.
-maman|Bravo, Aniss.
-narrateur|Aniss boit.
-narrateur|Une goutte coule sur son menton.</t>
+maman|Il était là, avec nous.
+narrateur|Aniss essuie la noix sur sa manche.
+narrateur|La manche sent le tilleul.
+maman|On la pose dans le sac ?
+enfant-m|Près du pain.
+narrateur|Le square s'ombre un peu.
+narrateur|Les tilleuls bougent, tout lents.</t>
         </is>
       </c>
     </row>
@@ -1960,12 +1964,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Les plots bleus restent dans la cour. J'ai fait un chemin. Oui. Puis un gâteau de sable. Dans l'espace montré. Bravo, Aniss.</t>
+          <t>La coque de noix brille dans le sac. Il a traversé. Oui. Les tilleuls sentent encore le miel. L'eau de la fontaine tremble, calme.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Les plots bleus restent dans la cour. J'ai fait un chemin. Oui. Puis un gâteau de sable. Dans l'espace montré. Bravo, Aniss.</t>
+          <t>La coque de noix brille dans le sac. Il a traversé. Oui. Les tilleuls sentent encore le miel. L'eau de la fontaine tremble, calme.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2028,7 +2032,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2100,12 +2104,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Les plots bleus restent dans la cour.
-enfant-m|J'ai fait un chemin.
+          <t>narrateur|La coque de noix brille dans le sac.
+enfant-m|Il a traversé.
 maman|Oui.
-maman|Puis un gâteau de sable.
-maman|Dans l'espace montré.
-maman|Bravo, Aniss.</t>
+narrateur|Les tilleuls sentent encore le miel.
+narrateur|L'eau de la fontaine tremble, calme.</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2176,6 +2179,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
